--- a/Data/18_FeSources/FeSources.xlsx
+++ b/Data/18_FeSources/FeSources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/hannah_cox_education_gov_uk/Documents/Documents/Projects/lsip_dashboard/Data/18_FeSources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{2D3A2B6E-EAB5-4658-ABD9-7280747BA78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7297E987-FB5B-4F30-A6A2-190410A21B14}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{2D3A2B6E-EAB5-4658-ABD9-7280747BA78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F166A94-924C-4BAF-89D4-CB129054AA13}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1065" yWindow="1185" windowWidth="5400" windowHeight="2813" xr2:uid="{A5D4C3F6-9CE9-44C0-BBBD-467D1E450A34}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14595" xr2:uid="{A5D4C3F6-9CE9-44C0-BBBD-467D1E450A34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Source</t>
   </si>
@@ -128,17 +128,46 @@
     <t>AoC</t>
   </si>
   <si>
-    <t>Working Futures 20235</t>
+    <t>Skills Imperative 2035</t>
+  </si>
+  <si>
+    <t>NEET and participation</t>
+  </si>
+  <si>
+    <t>Young people’s participation in education, employment and training and those not in education, employment or training (NEET). NEET age 16 to 24 and Local Authorty Figures</t>
+  </si>
+  <si>
+    <t>Statistics: NEET and participation - GOV.UK (www.gov.uk)</t>
+  </si>
+  <si>
+    <t>Publicaly available</t>
+  </si>
+  <si>
+    <t>Something from HESA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0B0C0C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -161,13 +190,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -480,17 +513,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{455C0F38-06FA-4C4D-8065-41AFD4764DD8}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="114.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="20.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -507,7 +540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -521,7 +554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -538,7 +571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -555,7 +588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -572,7 +605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -589,7 +622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -606,12 +639,38 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" display="https://www.gov.uk/government/collections/statistics-neet" xr:uid="{01C3C342-CACD-49B2-8D21-9970CC01C43E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>